--- a/data/trans_dic/KIDMED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Estudios-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,25</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,1</t>
+          <t>0,3; 6,53</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,0</t>
+          <t>1,79; 4,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,08</t>
+          <t>1,65; 4,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,95</t>
+          <t>1,95; 4,01</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,28</t>
+          <t>2,02; 7,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,49</t>
+          <t>1,09; 6,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,24</t>
+          <t>2,14; 6,27</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,77</t>
+          <t>2,1; 4,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,77</t>
+          <t>1,78; 4,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,91</t>
+          <t>2,27; 3,94</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>596</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1791</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2515</t>
+          <t>0; 5612</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4814</t>
+          <t>0; 2976</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>431; 5716</t>
+          <t>299; 6507</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15661</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27099</t>
+          <t>25828</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6524; 18070</t>
+          <t>8371; 22744</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8993; 25686</t>
+          <t>7024; 17772</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18619; 37792</t>
+          <t>17350; 35696</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12201</t>
+          <t>12000</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1559; 9186</t>
+          <t>3364; 12834</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3388; 13559</t>
+          <t>1601; 9824</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7393; 20417</t>
+          <t>6731; 19664</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>16554</t>
+          <t>22371</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24530</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>39620</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10994; 24584</t>
+          <t>14389; 31658</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16282; 35530</t>
+          <t>11005; 25426</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30791; 54605</t>
+          <t>29610; 51442</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/KIDMED_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDMED_R2-Estudios-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,290 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Primarios</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,45</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,48</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 6,53</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,79; 4,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,65; 4,18</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,95; 4,01</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,3%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,02; 7,7</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,09; 6,68</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2,14; 6,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,1; 4,61</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,78; 4,12</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 3,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -828,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.02225351213495498</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.01298476261283332</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01798246180049159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>1195</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1791</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.00299869422770016</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5612</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2976</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>299; 6507</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1044849530699149</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.06482254496376207</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.06531830998204501</v>
       </c>
     </row>
     <row r="7">
@@ -901,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.03002178974255539</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.027846106010715</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.02898492472638254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>14003</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11825</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>25828</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01794641770193769</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01654043537728316</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01947085153459071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8371; 22744</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7024; 17772</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>17350; 35696</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04876294743262278</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.04184930060834242</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0400587052250975</v>
       </c>
     </row>
     <row r="10">
@@ -974,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.04303152630593636</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.03280925666011783</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03823872650187554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>7173</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4828</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>12000</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02018108677718191</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01088083966447896</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.02144667454509331</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3364; 12834</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>1601; 9824</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6731; 19664</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.07699597456654382</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.06676815179303926</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.06265976094117594</v>
       </c>
     </row>
     <row r="13">
@@ -1047,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.03257159219190062</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.02792392525977756</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.03037087277522908</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>22371</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17249</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39620</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.02095011880756617</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01781549404067172</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.02269788638959861</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>14389; 31658</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>11005; 25426</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29610; 51442</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.04609328257751053</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.04116110718927781</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.03943296221111315</v>
       </c>
     </row>
     <row r="16">
@@ -1129,4 +781,376 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen una baja adherencia a la dieta mediterránea (tasa de respuesta: 96,61%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1195</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>596</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>5612</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2976</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>6507</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>14003</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>11825</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>25828</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>8371</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>7024</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>17350</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>22744</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>17772</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>35696</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>7173</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>4828</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>3364</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>1601</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>6731</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>12834</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>9824</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>19664</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>22371</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>17249</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>39620</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>14389</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>11005</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>29610</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>31658</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>25426</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>51442</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>